--- a/data/anomali/agregat_anomali_usaha_per_kecamatan.xlsx
+++ b/data/anomali/agregat_anomali_usaha_per_kecamatan.xlsx
@@ -16,7 +16,7 @@
     <t>DATA RADAR ANOMALI USAHA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kecamatan | Dicetak: 1 Jul 2026, 11.37</t>
+    <t>Seluruh data sampai Kecamatan | Dicetak: 5 Jul 2026, 10.56</t>
   </si>
   <si>
     <t>Kode</t>
@@ -76,6 +76,18 @@
     <t>Persentase Anomali 4 - Sudah Tindak Lanjut</t>
   </si>
   <si>
+    <t>Anomali 6 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 6 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 6 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 6 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
     <t>Anomali 5 - Belum Tindak Lanjut</t>
   </si>
   <si>
@@ -88,18 +100,6 @@
     <t>Persentase Anomali 5 - Sudah Tindak Lanjut</t>
   </si>
   <si>
-    <t>Anomali 6 - Belum Tindak Lanjut</t>
-  </si>
-  <si>
-    <t>Persentase Anomali 6 - Belum Tindak Lanjut</t>
-  </si>
-  <si>
-    <t>Anomali 6 - Sudah Tindak Lanjut</t>
-  </si>
-  <si>
-    <t>Persentase Anomali 6 - Sudah Tindak Lanjut</t>
-  </si>
-  <si>
     <t>Anomali 7 - Belum Tindak Lanjut</t>
   </si>
   <si>
@@ -235,205 +235,205 @@
     <t>SULAWESI UTARA</t>
   </si>
   <si>
-    <t>53,76</t>
+    <t>6,23</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>13,27</t>
-  </si>
-  <si>
-    <t>0,66</t>
+    <t>1,31</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>7103</t>
+  </si>
+  <si>
+    <t>KEPULAUAN SANGIHE</t>
+  </si>
+  <si>
+    <t>7103040</t>
+  </si>
+  <si>
+    <t>MANGANITU SELATAN</t>
+  </si>
+  <si>
+    <t>7,98</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>90,96</t>
+  </si>
+  <si>
+    <t>7103041</t>
+  </si>
+  <si>
+    <t>TATOARENG</t>
+  </si>
+  <si>
+    <t>16,36</t>
+  </si>
+  <si>
+    <t>2,73</t>
+  </si>
+  <si>
+    <t>9,09</t>
+  </si>
+  <si>
+    <t>71,82</t>
+  </si>
+  <si>
+    <t>7103050</t>
+  </si>
+  <si>
+    <t>TAMAKO</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>98,03</t>
+  </si>
+  <si>
+    <t>7103060</t>
+  </si>
+  <si>
+    <t>TABUKAN SELATAN</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>98,4</t>
+  </si>
+  <si>
+    <t>7103061</t>
+  </si>
+  <si>
+    <t>TABUKAN SELATAN TENGAH</t>
+  </si>
+  <si>
+    <t>12,64</t>
+  </si>
+  <si>
+    <t>87,36</t>
+  </si>
+  <si>
+    <t>7103062</t>
+  </si>
+  <si>
+    <t>TABUKAN SELATAN TENGGARA</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>97,69</t>
+  </si>
+  <si>
+    <t>7103070</t>
+  </si>
+  <si>
+    <t>TABUKAN TENGAH</t>
+  </si>
+  <si>
+    <t>3,16</t>
+  </si>
+  <si>
+    <t>2,63</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>93,42</t>
+  </si>
+  <si>
+    <t>7103080</t>
+  </si>
+  <si>
+    <t>MANGANITU</t>
+  </si>
+  <si>
+    <t>3,36</t>
+  </si>
+  <si>
+    <t>96,64</t>
+  </si>
+  <si>
+    <t>7103090</t>
+  </si>
+  <si>
+    <t>TAHUNA</t>
+  </si>
+  <si>
+    <t>10,58</t>
+  </si>
+  <si>
+    <t>4,76</t>
+  </si>
+  <si>
+    <t>84,13</t>
+  </si>
+  <si>
+    <t>7103091</t>
+  </si>
+  <si>
+    <t>TAHUNA TIMUR</t>
+  </si>
+  <si>
+    <t>8,49</t>
+  </si>
+  <si>
+    <t>3,69</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>87,08</t>
+  </si>
+  <si>
+    <t>7103092</t>
+  </si>
+  <si>
+    <t>TAHUNA BARAT</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>97,14</t>
+  </si>
+  <si>
+    <t>7103100</t>
+  </si>
+  <si>
+    <t>TABUKAN UTARA</t>
+  </si>
+  <si>
+    <t>4,85</t>
+  </si>
+  <si>
+    <t>1,08</t>
   </si>
   <si>
     <t>0,11</t>
   </si>
   <si>
-    <t>32,08</t>
-  </si>
-  <si>
-    <t>7103</t>
-  </si>
-  <si>
-    <t>KEPULAUAN SANGIHE</t>
-  </si>
-  <si>
-    <t>7103040</t>
-  </si>
-  <si>
-    <t>MANGANITU SELATAN</t>
-  </si>
-  <si>
-    <t>36,41</t>
-  </si>
-  <si>
-    <t>26,27</t>
-  </si>
-  <si>
-    <t>37,33</t>
-  </si>
-  <si>
-    <t>7103041</t>
-  </si>
-  <si>
-    <t>TATOARENG</t>
-  </si>
-  <si>
-    <t>30,77</t>
-  </si>
-  <si>
-    <t>38,46</t>
-  </si>
-  <si>
-    <t>11,54</t>
-  </si>
-  <si>
-    <t>19,23</t>
-  </si>
-  <si>
-    <t>7103050</t>
-  </si>
-  <si>
-    <t>TAMAKO</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>6,67</t>
-  </si>
-  <si>
-    <t>3,33</t>
-  </si>
-  <si>
-    <t>7103060</t>
-  </si>
-  <si>
-    <t>TABUKAN SELATAN</t>
-  </si>
-  <si>
-    <t>34,78</t>
-  </si>
-  <si>
-    <t>1,45</t>
-  </si>
-  <si>
-    <t>63,77</t>
-  </si>
-  <si>
-    <t>7103061</t>
-  </si>
-  <si>
-    <t>TABUKAN SELATAN TENGAH</t>
-  </si>
-  <si>
-    <t>52,38</t>
-  </si>
-  <si>
-    <t>4,76</t>
-  </si>
-  <si>
-    <t>38,1</t>
-  </si>
-  <si>
-    <t>7103062</t>
-  </si>
-  <si>
-    <t>TABUKAN SELATAN TENGGARA</t>
-  </si>
-  <si>
-    <t>41,03</t>
-  </si>
-  <si>
-    <t>58,97</t>
-  </si>
-  <si>
-    <t>7103070</t>
-  </si>
-  <si>
-    <t>TABUKAN TENGAH</t>
-  </si>
-  <si>
-    <t>28,21</t>
-  </si>
-  <si>
-    <t>5,13</t>
-  </si>
-  <si>
-    <t>7103080</t>
-  </si>
-  <si>
-    <t>MANGANITU</t>
-  </si>
-  <si>
-    <t>63,01</t>
-  </si>
-  <si>
-    <t>17,81</t>
-  </si>
-  <si>
-    <t>19,18</t>
-  </si>
-  <si>
-    <t>7103090</t>
-  </si>
-  <si>
-    <t>TAHUNA</t>
-  </si>
-  <si>
-    <t>64,86</t>
-  </si>
-  <si>
-    <t>10,81</t>
-  </si>
-  <si>
-    <t>24,32</t>
-  </si>
-  <si>
-    <t>7103091</t>
-  </si>
-  <si>
-    <t>TAHUNA TIMUR</t>
-  </si>
-  <si>
-    <t>61,22</t>
-  </si>
-  <si>
-    <t>24,49</t>
-  </si>
-  <si>
-    <t>14,29</t>
-  </si>
-  <si>
-    <t>7103092</t>
-  </si>
-  <si>
-    <t>TAHUNA BARAT</t>
-  </si>
-  <si>
-    <t>37,5</t>
-  </si>
-  <si>
-    <t>6,25</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>7103100</t>
-  </si>
-  <si>
-    <t>TABUKAN UTARA</t>
-  </si>
-  <si>
-    <t>72,6</t>
-  </si>
-  <si>
-    <t>2,28</t>
-  </si>
-  <si>
-    <t>25,11</t>
+    <t>93,97</t>
   </si>
   <si>
     <t>7103101</t>
@@ -442,10 +442,10 @@
     <t>NUSA TABUKAN</t>
   </si>
   <si>
-    <t>70,83</t>
-  </si>
-  <si>
-    <t>29,17</t>
+    <t>16,43</t>
+  </si>
+  <si>
+    <t>83,57</t>
   </si>
   <si>
     <t>7103102</t>
@@ -454,10 +454,10 @@
     <t>KEPULAUAN MARORE</t>
   </si>
   <si>
-    <t>83,33</t>
-  </si>
-  <si>
-    <t>16,67</t>
+    <t>12,69</t>
+  </si>
+  <si>
+    <t>87,31</t>
   </si>
   <si>
     <t>7103110</t>
@@ -466,13 +466,13 @@
     <t>KENDAHE</t>
   </si>
   <si>
-    <t>48,72</t>
-  </si>
-  <si>
-    <t>7,69</t>
-  </si>
-  <si>
-    <t>43,59</t>
+    <t>9,84</t>
+  </si>
+  <si>
+    <t>2,19</t>
+  </si>
+  <si>
+    <t>87,98</t>
   </si>
   <si>
     <t/>
@@ -1346,10 +1346,10 @@
         <v>73</v>
       </c>
       <c r="C6" s="7">
-        <v>904</v>
+        <v>3674</v>
       </c>
       <c r="D6" s="7">
-        <v>486</v>
+        <v>229</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>74</v>
@@ -1361,7 +1361,7 @@
         <v>75</v>
       </c>
       <c r="H6" s="7">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>76</v>
@@ -1373,7 +1373,7 @@
         <v>75</v>
       </c>
       <c r="L6" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>77</v>
@@ -1385,10 +1385,10 @@
         <v>75</v>
       </c>
       <c r="P6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R6" s="7">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>75</v>
       </c>
       <c r="T6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="V6" s="7">
         <v>0</v>
@@ -1409,10 +1409,10 @@
         <v>75</v>
       </c>
       <c r="X6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Z6" s="7">
         <v>0</v>
@@ -1421,10 +1421,10 @@
         <v>75</v>
       </c>
       <c r="AB6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AD6" s="7">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>75</v>
       </c>
       <c r="AF6" s="7">
-        <v>290</v>
+        <v>3380</v>
       </c>
       <c r="AG6" s="8" t="s">
         <v>79</v>
@@ -1453,10 +1453,10 @@
         <v>81</v>
       </c>
       <c r="C7" s="7">
-        <v>904</v>
+        <v>3674</v>
       </c>
       <c r="D7" s="7">
-        <v>486</v>
+        <v>229</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>74</v>
@@ -1468,7 +1468,7 @@
         <v>75</v>
       </c>
       <c r="H7" s="7">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>76</v>
@@ -1480,7 +1480,7 @@
         <v>75</v>
       </c>
       <c r="L7" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>77</v>
@@ -1492,10 +1492,10 @@
         <v>75</v>
       </c>
       <c r="P7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -1504,10 +1504,10 @@
         <v>75</v>
       </c>
       <c r="T7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="V7" s="7">
         <v>0</v>
@@ -1516,10 +1516,10 @@
         <v>75</v>
       </c>
       <c r="X7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Z7" s="7">
         <v>0</v>
@@ -1528,10 +1528,10 @@
         <v>75</v>
       </c>
       <c r="AB7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AD7" s="7">
         <v>0</v>
@@ -1540,7 +1540,7 @@
         <v>75</v>
       </c>
       <c r="AF7" s="7">
-        <v>290</v>
+        <v>3380</v>
       </c>
       <c r="AG7" s="8" t="s">
         <v>79</v>
@@ -1560,10 +1560,10 @@
         <v>83</v>
       </c>
       <c r="C8" s="10">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="D8" s="10">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>84</v>
@@ -1575,7 +1575,7 @@
         <v>75</v>
       </c>
       <c r="H8" s="10">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>85</v>
@@ -1647,7 +1647,7 @@
         <v>75</v>
       </c>
       <c r="AF8" s="10">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AG8" s="11" t="s">
         <v>86</v>
@@ -1667,10 +1667,10 @@
         <v>88</v>
       </c>
       <c r="C9" s="10">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="D9" s="10">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>89</v>
@@ -1682,7 +1682,7 @@
         <v>75</v>
       </c>
       <c r="H9" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>90</v>
@@ -1694,7 +1694,7 @@
         <v>75</v>
       </c>
       <c r="L9" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>91</v>
@@ -1754,7 +1754,7 @@
         <v>75</v>
       </c>
       <c r="AF9" s="10">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="AG9" s="11" t="s">
         <v>92</v>
@@ -1774,10 +1774,10 @@
         <v>94</v>
       </c>
       <c r="C10" s="10">
-        <v>30</v>
+        <v>203</v>
       </c>
       <c r="D10" s="10">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>95</v>
@@ -1789,82 +1789,82 @@
         <v>75</v>
       </c>
       <c r="H10" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10" s="10">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T10" s="10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V10" s="10">
+        <v>0</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF10" s="10">
+        <v>199</v>
+      </c>
+      <c r="AG10" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="J10" s="10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N10" s="10">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P10" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R10" s="10">
-        <v>0</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T10" s="10">
-        <v>0</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V10" s="10">
-        <v>0</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X10" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="AH10" s="10">
         <v>0</v>
@@ -1875,103 +1875,103 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="10">
+        <v>250</v>
+      </c>
+      <c r="D11" s="10">
+        <v>4</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="10">
-        <v>69</v>
-      </c>
-      <c r="D11" s="10">
-        <v>24</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R11" s="10">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T11" s="10">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V11" s="10">
+        <v>0</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF11" s="10">
+        <v>246</v>
+      </c>
+      <c r="AG11" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R11" s="10">
-        <v>0</v>
-      </c>
-      <c r="S11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V11" s="10">
-        <v>0</v>
-      </c>
-      <c r="W11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF11" s="10">
-        <v>44</v>
-      </c>
-      <c r="AG11" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="AH11" s="10">
         <v>0</v>
@@ -1982,19 +1982,19 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C12" s="10">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="D12" s="10">
         <v>11</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F12" s="10">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         <v>75</v>
       </c>
       <c r="H12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="J12" s="10">
         <v>0</v>
@@ -2015,10 +2015,10 @@
         <v>75</v>
       </c>
       <c r="L12" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="N12" s="10">
         <v>0</v>
@@ -2075,10 +2075,10 @@
         <v>75</v>
       </c>
       <c r="AF12" s="10">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="AG12" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AH12" s="10">
         <v>0</v>
@@ -2089,103 +2089,103 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="10">
+        <v>130</v>
+      </c>
+      <c r="D13" s="10">
+        <v>3</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R13" s="10">
+        <v>0</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T13" s="10">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V13" s="10">
+        <v>0</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>127</v>
+      </c>
+      <c r="AG13" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="10">
-        <v>39</v>
-      </c>
-      <c r="D13" s="10">
-        <v>16</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" s="10">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P13" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R13" s="10">
-        <v>0</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V13" s="10">
-        <v>0</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X13" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF13" s="10">
-        <v>23</v>
-      </c>
-      <c r="AG13" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="AH13" s="10">
         <v>0</v>
@@ -2196,31 +2196,31 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="10">
+        <v>380</v>
+      </c>
+      <c r="D14" s="10">
+        <v>12</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="10">
+        <v>10</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="10">
-        <v>39</v>
-      </c>
-      <c r="D14" s="10">
-        <v>15</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="10">
-        <v>11</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="J14" s="10">
         <v>0</v>
@@ -2232,67 +2232,67 @@
         <v>2</v>
       </c>
       <c r="M14" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P14" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R14" s="10">
+        <v>0</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T14" s="10">
+        <v>1</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="V14" s="10">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X14" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF14" s="10">
+        <v>355</v>
+      </c>
+      <c r="AG14" s="11" t="s">
         <v>115</v>
-      </c>
-      <c r="N14" s="10">
-        <v>0</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P14" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R14" s="10">
-        <v>0</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T14" s="10">
-        <v>0</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V14" s="10">
-        <v>0</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X14" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF14" s="10">
-        <v>11</v>
-      </c>
-      <c r="AG14" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="AH14" s="10">
         <v>0</v>
@@ -2309,10 +2309,10 @@
         <v>117</v>
       </c>
       <c r="C15" s="10">
-        <v>73</v>
+        <v>446</v>
       </c>
       <c r="D15" s="10">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>118</v>
@@ -2324,82 +2324,82 @@
         <v>75</v>
       </c>
       <c r="H15" s="10">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R15" s="10">
+        <v>0</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T15" s="10">
+        <v>0</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V15" s="10">
+        <v>0</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF15" s="10">
+        <v>431</v>
+      </c>
+      <c r="AG15" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N15" s="10">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R15" s="10">
-        <v>0</v>
-      </c>
-      <c r="S15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V15" s="10">
-        <v>0</v>
-      </c>
-      <c r="W15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF15" s="10">
-        <v>14</v>
-      </c>
-      <c r="AG15" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="AH15" s="10">
         <v>0</v>
@@ -2410,103 +2410,103 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="10">
+        <v>189</v>
+      </c>
+      <c r="D16" s="10">
+        <v>20</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="10">
-        <v>37</v>
-      </c>
-      <c r="D16" s="10">
-        <v>24</v>
-      </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="10">
+        <v>9</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="10">
-        <v>0</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="10">
-        <v>4</v>
-      </c>
-      <c r="I16" s="11" t="s">
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L16" s="10">
+        <v>1</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R16" s="10">
+        <v>0</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T16" s="10">
+        <v>0</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V16" s="10">
+        <v>0</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF16" s="10">
+        <v>159</v>
+      </c>
+      <c r="AG16" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L16" s="10">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N16" s="10">
-        <v>0</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P16" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R16" s="10">
-        <v>0</v>
-      </c>
-      <c r="S16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T16" s="10">
-        <v>0</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V16" s="10">
-        <v>0</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X16" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF16" s="10">
-        <v>9</v>
-      </c>
-      <c r="AG16" s="11" t="s">
-        <v>125</v>
       </c>
       <c r="AH16" s="10">
         <v>0</v>
@@ -2517,44 +2517,44 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="10">
+        <v>271</v>
+      </c>
+      <c r="D17" s="10">
+        <v>23</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="10">
-        <v>49</v>
-      </c>
-      <c r="D17" s="10">
-        <v>30</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="F17" s="10">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="10">
+        <v>10</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="10">
-        <v>0</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="10">
-        <v>12</v>
-      </c>
-      <c r="I17" s="11" t="s">
+      <c r="J17" s="10">
+        <v>0</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L17" s="10">
+        <v>2</v>
+      </c>
+      <c r="M17" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="J17" s="10">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L17" s="10">
-        <v>0</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="N17" s="10">
         <v>0</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>75</v>
       </c>
       <c r="AF17" s="10">
-        <v>7</v>
+        <v>236</v>
       </c>
       <c r="AG17" s="11" t="s">
         <v>130</v>
@@ -2630,10 +2630,10 @@
         <v>132</v>
       </c>
       <c r="C18" s="10">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D18" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>133</v>
@@ -2693,34 +2693,34 @@
         <v>75</v>
       </c>
       <c r="X18" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF18" s="10">
+        <v>34</v>
+      </c>
+      <c r="AG18" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="Z18" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB18" s="10">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD18" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF18" s="10">
-        <v>8</v>
-      </c>
-      <c r="AG18" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="AH18" s="10">
         <v>0</v>
@@ -2731,56 +2731,56 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="10">
+        <v>928</v>
+      </c>
+      <c r="D19" s="10">
+        <v>45</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="10">
-        <v>219</v>
-      </c>
-      <c r="D19" s="10">
-        <v>159</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="F19" s="10">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="10">
+        <v>10</v>
+      </c>
+      <c r="I19" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="F19" s="10">
-        <v>0</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="10">
-        <v>5</v>
-      </c>
-      <c r="I19" s="11" t="s">
+      <c r="J19" s="10">
+        <v>0</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="10">
+        <v>0</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P19" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="J19" s="10">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19" s="10">
-        <v>0</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N19" s="10">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P19" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="R19" s="10">
         <v>0</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>75</v>
       </c>
       <c r="AF19" s="10">
-        <v>55</v>
+        <v>872</v>
       </c>
       <c r="AG19" s="11" t="s">
         <v>140</v>
@@ -2844,10 +2844,10 @@
         <v>142</v>
       </c>
       <c r="C20" s="10">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="D20" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>143</v>
@@ -2931,7 +2931,7 @@
         <v>75</v>
       </c>
       <c r="AF20" s="10">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="AG20" s="11" t="s">
         <v>144</v>
@@ -2951,10 +2951,10 @@
         <v>146</v>
       </c>
       <c r="C21" s="10">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D21" s="10">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>147</v>
@@ -2966,82 +2966,82 @@
         <v>75</v>
       </c>
       <c r="H21" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J21" s="10">
+        <v>0</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R21" s="10">
+        <v>0</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="T21" s="10">
+        <v>0</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V21" s="10">
+        <v>0</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF21" s="10">
+        <v>117</v>
+      </c>
+      <c r="AG21" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="J21" s="10">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L21" s="10">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21" s="10">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P21" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R21" s="10">
-        <v>0</v>
-      </c>
-      <c r="S21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="V21" s="10">
-        <v>0</v>
-      </c>
-      <c r="W21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="X21" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF21" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="AH21" s="10">
         <v>0</v>
@@ -3058,10 +3058,10 @@
         <v>150</v>
       </c>
       <c r="C22" s="10">
-        <v>39</v>
+        <v>183</v>
       </c>
       <c r="D22" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>151</v>
@@ -3073,7 +3073,7 @@
         <v>75</v>
       </c>
       <c r="H22" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>152</v>
@@ -3145,7 +3145,7 @@
         <v>75</v>
       </c>
       <c r="AF22" s="10">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="AG22" s="11" t="s">
         <v>153</v>
@@ -3165,10 +3165,10 @@
         <v>155</v>
       </c>
       <c r="C23" s="13">
-        <v>904</v>
+        <v>3674</v>
       </c>
       <c r="D23" s="13">
-        <v>486</v>
+        <v>229</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>74</v>
@@ -3180,7 +3180,7 @@
         <v>75</v>
       </c>
       <c r="H23" s="13">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>76</v>
@@ -3192,7 +3192,7 @@
         <v>75</v>
       </c>
       <c r="L23" s="13">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M23" s="14" t="s">
         <v>77</v>
@@ -3204,10 +3204,10 @@
         <v>75</v>
       </c>
       <c r="P23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R23" s="13">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         <v>75</v>
       </c>
       <c r="T23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="V23" s="13">
         <v>0</v>
@@ -3228,10 +3228,10 @@
         <v>75</v>
       </c>
       <c r="X23" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Z23" s="13">
         <v>0</v>
@@ -3240,10 +3240,10 @@
         <v>75</v>
       </c>
       <c r="AB23" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AD23" s="13">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>75</v>
       </c>
       <c r="AF23" s="13">
-        <v>290</v>
+        <v>3380</v>
       </c>
       <c r="AG23" s="14" t="s">
         <v>79</v>
